--- a/data/trans_orig/IP16A11_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP16A11_2023-Provincia-trans_orig.xlsx
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>1953</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10146</t>
+          <t>10049</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>33,39%</t>
+          <t>33,07%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1433</t>
+          <t>1183</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9195</t>
+          <t>9119</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>41,19%</t>
+          <t>40,85%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5549</t>
+          <t>5259</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>15947</t>
+          <t>17241</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>30,26%</t>
+          <t>32,71%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>20238</t>
+          <t>20335</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>28384</t>
+          <t>28431</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>66,61%</t>
+          <t>66,93%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>93,42%</t>
+          <t>93,57%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>13127</t>
+          <t>13203</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>20889</t>
+          <t>21139</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>58,81%</t>
+          <t>59,15%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,58%</t>
+          <t>94,7%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>36759</t>
+          <t>35465</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>47157</t>
+          <t>47447</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>69,74%</t>
+          <t>67,29%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>89,47%</t>
+          <t>90,02%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7204</t>
+          <t>7322</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>44640</t>
+          <t>44694</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>11,49%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>70,03%</t>
+          <t>70,12%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>21817</t>
+          <t>22167</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>33882</t>
+          <t>33807</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>45,3%</t>
+          <t>46,02%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>70,35%</t>
+          <t>70,19%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>19484</t>
+          <t>24035</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>71328</t>
+          <t>71150</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>21,48%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>63,74%</t>
+          <t>63,58%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>19103</t>
+          <t>19049</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>56539</t>
+          <t>56421</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>29,97%</t>
+          <t>29,88%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>88,7%</t>
+          <t>88,51%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>14281</t>
+          <t>14356</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>26346</t>
+          <t>25996</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>29,65%</t>
+          <t>29,81%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>54,7%</t>
+          <t>53,98%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>40578</t>
+          <t>40756</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>92422</t>
+          <t>87871</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>36,26%</t>
+          <t>36,42%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>82,59%</t>
+          <t>78,52%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1356</t>
+          <t>1285</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6990</t>
+          <t>7203</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>38,09%</t>
+          <t>39,26%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1372</t>
+          <t>1318</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>7635</t>
+          <t>7611</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>19,76%</t>
+          <t>19,7%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11359</t>
+          <t>11146</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>16993</t>
+          <t>17064</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>61,91%</t>
+          <t>60,74%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>92,61%</t>
+          <t>93,0%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>31000</t>
+          <t>31024</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>37263</t>
+          <t>37317</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>80,24%</t>
+          <t>80,3%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,45%</t>
+          <t>96,59%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2236</t>
+          <t>2055</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8359</t>
+          <t>8305</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,86%</t>
+          <t>16,42%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>66,76%</t>
+          <t>66,33%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1251</t>
+          <t>1312</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7810</t>
+          <t>7903</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>70,53%</t>
+          <t>71,37%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,7 +1829,7 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4853</t>
+          <t>5065</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>20,57%</t>
+          <t>21,47%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>59,77%</t>
+          <t>59,78%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>4162</t>
+          <t>4216</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>10285</t>
+          <t>10466</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>33,24%</t>
+          <t>33,67%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>82,14%</t>
+          <t>83,58%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3263</t>
+          <t>3170</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>9822</t>
+          <t>9761</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>29,47%</t>
+          <t>28,63%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>88,7%</t>
+          <t>88,15%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1947,7 +1947,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>18740</t>
+          <t>18528</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>40,23%</t>
+          <t>40,22%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>79,43%</t>
+          <t>78,53%</t>
         </is>
       </c>
     </row>
@@ -2102,12 +2102,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1084</t>
+          <t>1021</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4951</t>
+          <t>4812</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,12 +2117,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>56,41%</t>
+          <t>54,82%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>459</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4403</t>
+          <t>4810</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>39,33%</t>
+          <t>42,96%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2396</t>
+          <t>2040</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>8225</t>
+          <t>7958</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>41,18%</t>
+          <t>39,84%</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3826</t>
+          <t>3965</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>7693</t>
+          <t>7756</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>43,59%</t>
+          <t>45,18%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>87,65%</t>
+          <t>88,37%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>6794</t>
+          <t>6387</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>11197</t>
+          <t>10738</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>60,67%</t>
+          <t>57,04%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>95,9%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>11749</t>
+          <t>12016</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>17578</t>
+          <t>17934</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>58,82%</t>
+          <t>60,16%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>88,0%</t>
+          <t>89,78%</t>
         </is>
       </c>
     </row>
@@ -2445,12 +2445,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>527</t>
+          <t>546</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4242</t>
+          <t>4426</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2460,12 +2460,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>55,24%</t>
+          <t>57,64%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2485,7 +2485,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>2973</t>
+          <t>2951</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2500,7 +2500,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>21,85%</t>
+          <t>21,69%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2515,12 +2515,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1036</t>
+          <t>1093</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>6400</t>
+          <t>6056</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>30,06%</t>
+          <t>28,45%</t>
         </is>
       </c>
     </row>
@@ -2558,12 +2558,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>3437</t>
+          <t>3253</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>7152</t>
+          <t>7133</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2573,12 +2573,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>44,76%</t>
+          <t>42,36%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>93,14%</t>
+          <t>92,89%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2593,7 +2593,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>10634</t>
+          <t>10656</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -2608,7 +2608,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>78,15%</t>
+          <t>78,31%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>14887</t>
+          <t>15231</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>20251</t>
+          <t>20194</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2643,12 +2643,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>69,94%</t>
+          <t>71,55%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,13%</t>
+          <t>94,87%</t>
         </is>
       </c>
     </row>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>8147</t>
+          <t>8234</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>16756</t>
+          <t>16796</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>27,35%</t>
+          <t>27,64%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>56,25%</t>
+          <t>56,39%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>11345</t>
+          <t>11290</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>23471</t>
+          <t>24160</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>25,58%</t>
+          <t>25,45%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>52,92%</t>
+          <t>54,47%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>22136</t>
+          <t>21374</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>38374</t>
+          <t>38443</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>29,86%</t>
+          <t>28,83%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>51,76%</t>
+          <t>51,85%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>13030</t>
+          <t>12990</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>21639</t>
+          <t>21552</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>43,75%</t>
+          <t>43,61%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>72,65%</t>
+          <t>72,36%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>20883</t>
+          <t>20194</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>33009</t>
+          <t>33064</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>47,08%</t>
+          <t>45,53%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>74,42%</t>
+          <t>74,55%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>35766</t>
+          <t>35697</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>52004</t>
+          <t>52766</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>48,24%</t>
+          <t>48,15%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>70,14%</t>
+          <t>71,17%</t>
         </is>
       </c>
     </row>
@@ -3131,12 +3131,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>477</t>
+          <t>777</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>4465</t>
+          <t>4563</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3146,12 +3146,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>55,04%</t>
+          <t>56,24%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3171,7 +3171,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>5314</t>
+          <t>4845</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3186,7 +3186,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>45,4%</t>
+          <t>41,39%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1706</t>
+          <t>1596</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>7715</t>
+          <t>8178</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3216,12 +3216,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>38,93%</t>
+          <t>41,26%</t>
         </is>
       </c>
     </row>
@@ -3244,12 +3244,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3648</t>
+          <t>3550</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>7636</t>
+          <t>7336</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3259,12 +3259,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>44,96%</t>
+          <t>43,76%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>94,12%</t>
+          <t>90,42%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3279,7 +3279,7 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>6393</t>
+          <t>6862</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
@@ -3294,7 +3294,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>54,6%</t>
+          <t>58,61%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>12104</t>
+          <t>11641</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>18113</t>
+          <t>18223</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>61,07%</t>
+          <t>58,74%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>91,39%</t>
+          <t>91,95%</t>
         </is>
       </c>
     </row>
@@ -3474,12 +3474,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>33793</t>
+          <t>35717</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>72844</t>
+          <t>73114</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>19,91%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>40,62%</t>
+          <t>40,77%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3509,12 +3509,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>48224</t>
+          <t>47794</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>71335</t>
+          <t>69961</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3524,12 +3524,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>26,39%</t>
+          <t>26,16%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>39,04%</t>
+          <t>38,29%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3544,12 +3544,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>86219</t>
+          <t>90094</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>133730</t>
+          <t>134078</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3559,12 +3559,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>23,81%</t>
+          <t>24,88%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>36,94%</t>
+          <t>37,03%</t>
         </is>
       </c>
     </row>
@@ -3587,12 +3587,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>106508</t>
+          <t>106238</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>145559</t>
+          <t>143635</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3602,12 +3602,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>59,38%</t>
+          <t>59,23%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>81,16%</t>
+          <t>80,09%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3622,12 +3622,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>111374</t>
+          <t>112748</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>134485</t>
+          <t>134915</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3637,12 +3637,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>60,96%</t>
+          <t>61,71%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>73,61%</t>
+          <t>73,84%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3657,12 +3657,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>228331</t>
+          <t>227983</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>275842</t>
+          <t>271967</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3672,12 +3672,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>63,06%</t>
+          <t>62,97%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>76,19%</t>
+          <t>75,12%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP16A11_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP16A11_2023-Provincia-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>3540</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1229</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>7678</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>18,37%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>6,38%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>39,84%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>5407</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>1953</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>10049</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>17,8%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>6,43%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>33,07%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>4573</t>
+          <t>5173</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1183</t>
+          <t>2516</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9119</t>
+          <t>8941</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>20,49%</t>
+          <t>24,87%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>40,85%</t>
+          <t>42,99%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>9980</t>
+          <t>8713</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5259</t>
+          <t>5070</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>17241</t>
+          <t>14139</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>18,94%</t>
+          <t>21,74%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>32,71%</t>
+          <t>35,28%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>15733</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>11595</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>18044</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>81,63%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>60,16%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>93,62%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>24977</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>20335</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>28431</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>82,2%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>66,93%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>93,57%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>17749</t>
+          <t>15627</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>13203</t>
+          <t>11859</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>21139</t>
+          <t>18284</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>79,51%</t>
+          <t>75,13%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>59,15%</t>
+          <t>57,01%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,7%</t>
+          <t>87,9%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>42726</t>
+          <t>31360</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>35465</t>
+          <t>25934</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>47447</t>
+          <t>35003</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>81,06%</t>
+          <t>78,26%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>67,29%</t>
+          <t>64,72%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>90,02%</t>
+          <t>87,35%</t>
         </is>
       </c>
     </row>
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>19273</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>19273</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>19273</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>35</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>30384</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>30384</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>30384</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>22322</t>
+          <t>20800</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>22322</t>
+          <t>20800</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>22322</t>
+          <t>20800</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>52706</t>
+          <t>40073</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>52706</t>
+          <t>40073</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>52706</t>
+          <t>40073</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,72 +1063,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>24532</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>18766</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>29870</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>57,49%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>43,98%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>70,01%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>36</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>23680</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>7322</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>44694</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>37,15%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>11,49%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>70,12%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>27915</t>
+          <t>23339</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>22167</t>
+          <t>16781</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>33807</t>
+          <t>28851</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>57,96%</t>
+          <t>59,04%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>46,02%</t>
+          <t>42,45%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>70,19%</t>
+          <t>72,98%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>51595</t>
+          <t>47871</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>24035</t>
+          <t>39722</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>71150</t>
+          <t>55160</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>46,11%</t>
+          <t>58,24%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>21,48%</t>
+          <t>48,32%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>63,58%</t>
+          <t>67,1%</t>
         </is>
       </c>
     </row>
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>18136</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>12798</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>23902</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>42,51%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>29,99%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>56,02%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>40063</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>19049</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>56421</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>62,85%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>29,88%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>88,51%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>20248</t>
+          <t>16194</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>14356</t>
+          <t>10682</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>25996</t>
+          <t>22752</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>42,04%</t>
+          <t>40,96%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>29,81%</t>
+          <t>27,02%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>53,98%</t>
+          <t>57,55%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>60311</t>
+          <t>34330</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>40756</t>
+          <t>27041</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>87871</t>
+          <t>42479</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>53,89%</t>
+          <t>41,76%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>36,42%</t>
+          <t>32,9%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>78,52%</t>
+          <t>51,68%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>42668</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>42668</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>42668</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>56</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>63743</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>63743</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>63743</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>48163</t>
+          <t>39533</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>48163</t>
+          <t>39533</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>48163</t>
+          <t>39533</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>111906</t>
+          <t>82201</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>111906</t>
+          <t>82201</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>111906</t>
+          <t>82201</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,72 +1406,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>3741</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1285</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>7203</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>20,39%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>7,0%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>39,26%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3646</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1388</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6868</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>20,83%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>39,23%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>3741</t>
+          <t>3646</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1318</t>
+          <t>1304</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>7611</t>
+          <t>7279</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>19,7%</t>
+          <t>20,69%</t>
         </is>
       </c>
     </row>
@@ -1519,72 +1519,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>17679</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>14608</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>11146</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>17064</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>79,61%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>60,74%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>93,0%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>20287</t>
+          <t>13861</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>10639</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>16119</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>79,17%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>60,77%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>92,07%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>34894</t>
+          <t>31540</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>31024</t>
+          <t>27907</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>37317</t>
+          <t>33882</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>90,32%</t>
+          <t>89,64%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>80,3%</t>
+          <t>79,31%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,59%</t>
+          <t>96,29%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>17679</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>17679</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>17679</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>18349</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>18349</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>18349</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>20287</t>
+          <t>17507</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>20287</t>
+          <t>17507</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>20287</t>
+          <t>17507</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>38635</t>
+          <t>35186</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>38635</t>
+          <t>35186</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>38635</t>
+          <t>35186</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,72 +1749,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>4263</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>1168</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>7169</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>40,93%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>11,22%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>68,83%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>5014</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>2055</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>8305</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>40,05%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>16,42%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>66,33%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>4304</t>
+          <t>4403</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1312</t>
+          <t>1837</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7903</t>
+          <t>7471</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>38,87%</t>
+          <t>36,03%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>15,03%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>71,37%</t>
+          <t>61,12%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>9318</t>
+          <t>8666</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5065</t>
+          <t>4970</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>14103</t>
+          <t>13956</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>39,5%</t>
+          <t>38,28%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>21,47%</t>
+          <t>21,95%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>59,78%</t>
+          <t>61,65%</t>
         </is>
       </c>
     </row>
@@ -1862,72 +1862,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>6153</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>3247</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>9248</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>59,07%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>31,17%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>88,78%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>7507</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>4216</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>10466</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>59,95%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>33,67%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>83,58%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>6769</t>
+          <t>7820</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3170</t>
+          <t>4752</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>9761</t>
+          <t>10386</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>61,13%</t>
+          <t>63,97%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>28,63%</t>
+          <t>38,88%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>88,15%</t>
+          <t>84,97%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>14275</t>
+          <t>13973</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>9490</t>
+          <t>8683</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>18528</t>
+          <t>17669</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>60,5%</t>
+          <t>61,72%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>40,22%</t>
+          <t>38,35%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>78,53%</t>
+          <t>78,05%</t>
         </is>
       </c>
     </row>
@@ -1975,57 +1975,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>10416</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>10416</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>10416</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>12521</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>12521</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>12521</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>11073</t>
+          <t>12223</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>11073</t>
+          <t>12223</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>11073</t>
+          <t>12223</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>23593</t>
+          <t>22639</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>23593</t>
+          <t>22639</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>23593</t>
+          <t>22639</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2092,72 +2092,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>1924</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>508</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>4665</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>18,74%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>4,94%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>45,44%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>2807</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>1021</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>4812</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>31,98%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>11,63%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>54,82%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>1903</t>
+          <t>2951</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>459</t>
+          <t>1045</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4810</t>
+          <t>4869</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>32,74%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>42,96%</t>
+          <t>54,02%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>4710</t>
+          <t>4876</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2040</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>7958</t>
+          <t>8181</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>23,58%</t>
+          <t>25,29%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>39,84%</t>
+          <t>42,43%</t>
         </is>
       </c>
     </row>
@@ -2205,72 +2205,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>8343</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>5602</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>9759</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>81,26%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>54,56%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>95,06%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>5970</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>3965</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>7756</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>68,02%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>45,18%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>88,37%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>9294</t>
+          <t>6063</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>6387</t>
+          <t>4145</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>10738</t>
+          <t>7969</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>83,0%</t>
+          <t>67,26%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>57,04%</t>
+          <t>45,98%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,9%</t>
+          <t>88,41%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>15264</t>
+          <t>14405</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>12016</t>
+          <t>11100</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>17934</t>
+          <t>16899</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>76,42%</t>
+          <t>74,71%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>60,16%</t>
+          <t>57,57%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>89,78%</t>
+          <t>87,64%</t>
         </is>
       </c>
     </row>
@@ -2318,57 +2318,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>10267</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>10267</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>10267</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>8777</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>8777</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>8777</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>11197</t>
+          <t>9014</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>11197</t>
+          <t>9014</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>11197</t>
+          <t>9014</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>19974</t>
+          <t>19281</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>19974</t>
+          <t>19281</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>19974</t>
+          <t>19281</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2435,72 +2435,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>827</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>2920</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>7,23%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>25,52%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>1968</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>546</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>4426</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>25,63%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>7,11%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>57,64%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>917</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>607</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>2951</t>
+          <t>4392</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>26,24%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>21,69%</t>
+          <t>57,32%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>2885</t>
+          <t>2837</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1093</t>
+          <t>1080</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>6056</t>
+          <t>5817</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>14,86%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>28,45%</t>
+          <t>30,46%</t>
         </is>
       </c>
     </row>
@@ -2548,72 +2548,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>10611</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>8518</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>11438</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>92,77%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>74,48%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>5711</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>3253</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>7133</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>74,37%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>42,36%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>92,89%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>12690</t>
+          <t>5652</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>10656</t>
+          <t>3270</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>13607</t>
+          <t>7055</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>93,26%</t>
+          <t>73,76%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>78,31%</t>
+          <t>42,68%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>92,07%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>18402</t>
+          <t>16262</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>15231</t>
+          <t>13282</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>20194</t>
+          <t>18019</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>86,45%</t>
+          <t>85,14%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>71,55%</t>
+          <t>69,54%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>94,87%</t>
+          <t>94,35%</t>
         </is>
       </c>
     </row>
@@ -2661,57 +2661,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>11438</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>11438</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>11438</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>7679</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>7679</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>7679</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>13607</t>
+          <t>7662</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>13607</t>
+          <t>7662</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>13607</t>
+          <t>7662</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>21287</t>
+          <t>19099</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>21287</t>
+          <t>19099</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>21287</t>
+          <t>19099</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2778,72 +2778,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>15879</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>9895</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>22136</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>37,78%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>23,54%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>52,66%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>12267</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>8234</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>16796</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>41,18%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>12632</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>8367</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>17188</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>41,73%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
         <is>
           <t>27,64%</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>56,39%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>17184</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>11290</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>24160</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>38,74%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>25,45%</t>
-        </is>
-      </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>54,47%</t>
+          <t>56,79%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>29451</t>
+          <t>28510</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>21374</t>
+          <t>20830</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>38443</t>
+          <t>36915</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>39,72%</t>
+          <t>39,43%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>28,83%</t>
+          <t>28,81%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>51,85%</t>
+          <t>51,06%</t>
         </is>
       </c>
     </row>
@@ -2891,74 +2891,74 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>26154</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>19897</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>32138</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>62,22%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>47,34%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>76,46%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>17519</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>12990</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>21552</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>58,82%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>43,61%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>17636</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>13080</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>21901</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>58,27%</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>43,21%</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
         <is>
           <t>72,36%</t>
         </is>
       </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>27170</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>20194</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>33064</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>61,26%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>45,53%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>74,55%</t>
-        </is>
-      </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
           <t>56</t>
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>44689</t>
+          <t>43790</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>35697</t>
+          <t>35385</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>52766</t>
+          <t>51470</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>60,28%</t>
+          <t>60,57%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>48,15%</t>
+          <t>48,94%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>71,17%</t>
+          <t>71,19%</t>
         </is>
       </c>
     </row>
@@ -3004,57 +3004,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>42033</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>42033</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>42033</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>46</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>29786</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>29786</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>29786</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>44354</t>
+          <t>30268</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>44354</t>
+          <t>30268</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>44354</t>
+          <t>30268</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>74140</t>
+          <t>72300</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>74140</t>
+          <t>72300</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>74140</t>
+          <t>72300</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3121,72 +3121,72 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>1887</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>5398</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>16,12%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>46,11%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>2121</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>777</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>4563</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>26,14%</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>9,58%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>56,24%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>1773</t>
+          <t>2049</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>658</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>4845</t>
+          <t>4417</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>26,84%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>41,39%</t>
+          <t>57,87%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,22 +3196,22 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>3893</t>
+          <t>3937</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1596</t>
+          <t>1557</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>8178</t>
+          <t>7716</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>19,64%</t>
+          <t>20,35%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
@@ -3221,7 +3221,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>41,26%</t>
+          <t>39,89%</t>
         </is>
       </c>
     </row>
@@ -3234,72 +3234,72 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>9820</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>6309</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>11707</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>83,88%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>53,89%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>5992</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>3550</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>7336</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>73,86%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>43,76%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>90,42%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>9934</t>
+          <t>5585</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>6862</t>
+          <t>3217</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>11707</t>
+          <t>6976</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>84,86%</t>
+          <t>73,16%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>58,61%</t>
+          <t>42,13%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>91,38%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,27 +3309,27 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>15926</t>
+          <t>15404</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>11641</t>
+          <t>11625</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>18223</t>
+          <t>17784</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>80,36%</t>
+          <t>79,65%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>58,74%</t>
+          <t>60,11%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3347,57 +3347,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>11707</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>11707</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>11707</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>8113</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>8113</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>8113</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>11707</t>
+          <t>7634</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>11707</t>
+          <t>7634</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>11707</t>
+          <t>7634</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3422,17 +3422,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>19819</t>
+          <t>19341</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>19819</t>
+          <t>19341</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>19819</t>
+          <t>19341</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3464,72 +3464,72 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>52852</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>42683</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>63754</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>31,94%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>25,79%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>38,53%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>89</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>57005</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>35717</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>73114</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>31,78%</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>19,91%</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>40,77%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>58569</t>
+          <t>56204</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>47794</t>
+          <t>47419</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>69961</t>
+          <t>66158</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>32,06%</t>
+          <t>38,86%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>26,16%</t>
+          <t>32,78%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>38,29%</t>
+          <t>45,74%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,32 +3539,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>115574</t>
+          <t>109056</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>90094</t>
+          <t>93456</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>134078</t>
+          <t>121778</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>31,92%</t>
+          <t>35,17%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>24,88%</t>
+          <t>30,14%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>37,03%</t>
+          <t>39,27%</t>
         </is>
       </c>
     </row>
@@ -3577,72 +3577,72 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>171</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>112627</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>101725</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>122796</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>68,06%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>61,47%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>74,21%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>140</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>122347</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>106238</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>143635</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>68,22%</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>59,23%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>80,09%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>171</t>
-        </is>
-      </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>124140</t>
+          <t>88437</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>112748</t>
+          <t>78483</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>134915</t>
+          <t>97222</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>67,94%</t>
+          <t>61,14%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>61,71%</t>
+          <t>54,26%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>73,84%</t>
+          <t>67,22%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,32 +3652,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>246487</t>
+          <t>201064</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>227983</t>
+          <t>188342</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>271967</t>
+          <t>216664</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>68,08%</t>
+          <t>64,83%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>62,97%</t>
+          <t>60,73%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>75,12%</t>
+          <t>69,86%</t>
         </is>
       </c>
     </row>
@@ -3690,57 +3690,57 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>251</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>165479</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>165479</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>165479</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
           <t>229</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>179352</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>179352</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>179352</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>251</t>
-        </is>
-      </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>182709</t>
+          <t>144641</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>182709</t>
+          <t>144641</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>182709</t>
+          <t>144641</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3765,17 +3765,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>362061</t>
+          <t>310120</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>362061</t>
+          <t>310120</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>362061</t>
+          <t>310120</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
